--- a/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,3</t>
+          <t>-2,5; 5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,41</t>
+          <t>-5,22; 3,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 4,91</t>
+          <t>-12,92; 5,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,14</t>
+          <t>-100,0; 265,73</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 9,3</t>
+          <t>-2,33; 8,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 0,0</t>
+          <t>-9,56; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 4,46</t>
+          <t>-5,35; 4,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -0,92</t>
+          <t>-9,41; -0,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 2,89</t>
+          <t>-6,18; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 9,65</t>
+          <t>-5,75; 9,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -1,41</t>
+          <t>-8,34; -1,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,39</t>
+          <t>-2,77; 1,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,8</t>
+          <t>-1,54; 5,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,58</t>
+          <t>-100,0; 55,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -0,88</t>
+          <t>-8,23; -0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 5,67</t>
+          <t>-1,12; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 3,56</t>
+          <t>-9,57; 3,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,07</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 0,0</t>
+          <t>-11,31; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -0,38</t>
+          <t>-3,93; -0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,91</t>
+          <t>-1,27; 1,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,03</t>
+          <t>-2,15; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-85,75; 3,38</t>
+          <t>-89,28; -10,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 295,34</t>
+          <t>-63,95; 260,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,83; 131,68</t>
+          <t>-58,81; 147,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 5,25</t>
+          <t>-2,53; 4,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,45</t>
+          <t>-5,37; 3,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 5,62</t>
+          <t>-12,07; 5,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 265,73</t>
+          <t>-100,0; 207,61</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 8,95</t>
+          <t>-3,0; 9,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 0,0</t>
+          <t>-9,48; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 4,46</t>
+          <t>-5,42; 3,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -0,91</t>
+          <t>-8,96; -0,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 2,89</t>
+          <t>-7,09; 2,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 9,92</t>
+          <t>-5,44; 10,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -1,36</t>
+          <t>-8,74; -1,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,74</t>
+          <t>-2,76; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,23</t>
+          <t>-1,59; 5,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,89</t>
+          <t>-100,0; 20,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -0,87</t>
+          <t>-7,71; -0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,09</t>
+          <t>-1,19; 5,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 5,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 3,64</t>
+          <t>-9,42; 3,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 17,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 0,0</t>
+          <t>-12,41; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,43</t>
+          <t>-4,05; -0,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,94</t>
+          <t>-1,2; 1,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,16</t>
+          <t>-2,06; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-89,28; -10,23</t>
+          <t>-87,01; 8,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 260,03</t>
+          <t>-62,24; 252,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 147,21</t>
+          <t>-60,04; 136,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,03</t>
+          <t>-2,52; 5,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,41</t>
+          <t>-6,86; 3,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 5,75</t>
+          <t>-13,2; 4,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 207,61</t>
+          <t>-100,0; 227,14</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 9,33</t>
+          <t>-2,35; 9,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,0</t>
+          <t>-9,85; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,7</t>
+          <t>-5,43; 4,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -0,91</t>
+          <t>-9,11; -0,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,87</t>
+          <t>-6,31; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 10,37</t>
+          <t>-5,82; 9,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,74; -1,36</t>
+          <t>-8,32; -1,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,38</t>
+          <t>-2,76; 2,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,07</t>
+          <t>-2,02; 4,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 20,83</t>
+          <t>-100,0; 39,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; -0,87</t>
+          <t>-8,58; -0,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,89</t>
+          <t>-1,31; 5,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 3,62</t>
+          <t>-11,14; 3,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,11</t>
+          <t>0,0; 17,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 0,0</t>
+          <t>-13,44; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; -0,32</t>
+          <t>-3,89; -0,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,98</t>
+          <t>-1,09; 1,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,11</t>
+          <t>-2,1; 2,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-87,01; 8,25</t>
+          <t>-85,75; 3,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 252,31</t>
+          <t>-60,07; 295,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 136,72</t>
+          <t>-59,83; 131,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,143 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-45,54%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.08997673373597956</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.03522232459123656</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.880492208010922</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.07223694814384181</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.02048995528129319</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4554313264636485</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 5,3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,86; 3,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,2; 4,91</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 227,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.521855130119222</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.856290277368739</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.1995625629702</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.297842470794031</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.412879235100605</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.907253361150301</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>2.271421240655414</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>165,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-9,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 9,3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-9,85; 0,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,43; 4,46</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.896643907865363</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.795457782810144</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2405533345342416</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1.653272889648529</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.09256020362205404</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-23,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.348594565150464</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9.847245500162465</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.426726535860523</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,11; -0,92</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 2,89</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,82; 9,65</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.302321420919903</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.459266170005519</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +747,143 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-4,13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-86,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-41,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.355600613302333</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.4303510798489621</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.021016932886376</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2329419064652358</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.7578126391969633</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,32; -1,41</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,76; 2,39</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 4,8</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 39,58</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.105102862497615</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.311417897425415</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.824213249043931</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.9158518325646727</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.888451139608147</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.652884062190964</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>186,99%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-8,58; -0,88</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,31; 5,67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,39</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-4.12728171800712</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5602477185074852</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.371674679308163</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.8679029629933577</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4112154269207274</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.9753033866051956</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5,5</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-51,64%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.318671185446073</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.76356172880944</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.017007653758651</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-11,14; 3,56</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 17,07</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-13,44; 0,0</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-1.410193702547409</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.388808009525897</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.798840308050192</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.3958108069310494</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,34 +891,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-2,02</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-62,2%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-1,22%</t>
+      <c r="C16" s="5" t="n">
+        <v>-3.010043313036358</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.727391961837008</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.166161504550706</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1.869898289196981</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -1109,42 +916,198 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,89; -0,38</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 1,91</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 2,03</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-85,75; 3,38</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-60,07; 295,34</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-59,83; 131,68</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-8.582718379302245</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.308196210927483</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-0.8779247633856674</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.6739397337621</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.386508712010447</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.957359244738415</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>5.497840254248042</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-2.408382563676246</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.5164066441588669</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-11.13711284763277</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-13.43812895393901</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.558152071881185</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>17.06641493745774</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2.018604217887308</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.2751709744146026</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.03116711127799238</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.62196803877</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1913735326479101</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.01220405646525908</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.891522399062434</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.092194996309381</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.10010867058595</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.8575444733870121</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.6006982654885332</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.5983263972272912</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-0.3782914414643721</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.90675855563475</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.029083532541474</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.03384277030713115</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>2.953425903628071</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.31677876242927</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1116,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
